--- a/Projektleitung/ProjektStu.xlsx
+++ b/Projektleitung/ProjektStu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zeiss-my.sharepoint.com/personal/nico_hoehn_zeiss_com/Documents/Microsoft Teams-Chatdateien/desktop/Stu/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/02520db892aadeb1/Dokumente/GitHub/the-machine-learning-brick/Projektleitung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{B10DB337-5233-4793-ACC1-40FBA2BF6423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58D91F39-6401-4AAC-ABDE-E10831E32DBF}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{B10DB337-5233-4793-ACC1-40FBA2BF6423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74193646-3A02-4CAD-9B50-E954F26E9371}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DBC8F7FF-C9D8-41D1-8461-80D8FB4B8939}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DBC8F7FF-C9D8-41D1-8461-80D8FB4B8939}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="71">
   <si>
     <t>Vorgangsmodus</t>
   </si>
@@ -243,6 +243,25 @@
 - Gehäuse entwerfen
 - Gehäuse testen
 - Gehäuse optimieren</t>
+  </si>
+  <si>
+    <t>- Edge impulse Datei auf MC Spielen
+- Matlab Datei umwandeln  auf MC Spielen</t>
+  </si>
+  <si>
+    <t>verlängern aber MS ander stelle lassen</t>
+  </si>
+  <si>
+    <t>verlängern + Meilenstein</t>
+  </si>
+  <si>
+    <t>an ms erster testdatensatz hängen</t>
+  </si>
+  <si>
+    <t>an gehäause erstellen hängen</t>
+  </si>
+  <si>
+    <t>verschieben auf 2.6</t>
   </si>
 </sst>
 </file>
@@ -282,7 +301,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -298,6 +317,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -340,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -357,14 +388,36 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -381,6 +434,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -700,13 +757,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA75D93C-EB10-4079-8CE1-EDD47049ADD5}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="39.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -732,147 +789,150 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="8"/>
+      <c r="G2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="7">
         <v>1</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="2" t="s">
+      <c r="F4" s="8"/>
+      <c r="G4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="7">
         <v>3</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="11">
         <v>3</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="12" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="I6" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="11">
         <v>5</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+    </row>
+    <row r="8" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -894,11 +954,11 @@
       <c r="G8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -920,7 +980,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -942,11 +1002,11 @@
       <c r="G10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
@@ -968,7 +1028,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -992,7 +1052,7 @@
       </c>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1014,55 +1074,61 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="11">
         <v>5</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="16" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="I14" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="11">
         <v>13</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -1086,7 +1152,7 @@
       </c>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -1108,7 +1174,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
@@ -1132,7 +1198,7 @@
       </c>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -1152,33 +1218,39 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="11">
         <v>19</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="11" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I20" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -1199,6 +1271,9 @@
       </c>
       <c r="G21" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/Projektleitung/ProjektStu.xlsx
+++ b/Projektleitung/ProjektStu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/02520db892aadeb1/Dokumente/GitHub/the-machine-learning-brick/Projektleitung/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zeiss-my.sharepoint.com/personal/nico_hoehn_zeiss_com/Documents/Microsoft Teams-Chatdateien/desktop/Stu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{B10DB337-5233-4793-ACC1-40FBA2BF6423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74193646-3A02-4CAD-9B50-E954F26E9371}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{B10DB337-5233-4793-ACC1-40FBA2BF6423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FD1EC56-4219-4D38-814D-45A03D40906F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DBC8F7FF-C9D8-41D1-8461-80D8FB4B8939}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DBC8F7FF-C9D8-41D1-8461-80D8FB4B8939}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="66">
   <si>
     <t>Vorgangsmodus</t>
   </si>
@@ -247,21 +247,6 @@
   <si>
     <t>- Edge impulse Datei auf MC Spielen
 - Matlab Datei umwandeln  auf MC Spielen</t>
-  </si>
-  <si>
-    <t>verlängern aber MS ander stelle lassen</t>
-  </si>
-  <si>
-    <t>verlängern + Meilenstein</t>
-  </si>
-  <si>
-    <t>an ms erster testdatensatz hängen</t>
-  </si>
-  <si>
-    <t>an gehäause erstellen hängen</t>
-  </si>
-  <si>
-    <t>verschieben auf 2.6</t>
   </si>
 </sst>
 </file>
@@ -301,7 +286,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -317,18 +302,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -388,36 +361,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,10 +385,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -757,13 +704,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA75D93C-EB10-4079-8CE1-EDD47049ADD5}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="39.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,150 +736,147 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7" t="s">
+    <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="3" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="7" t="s">
+    <row r="5" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="2">
         <v>3</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="2">
         <v>3</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="11" t="s">
+    </row>
+    <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="2">
         <v>5</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -954,11 +898,11 @@
       <c r="G8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -980,7 +924,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -1002,11 +946,11 @@
       <c r="G10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
@@ -1028,7 +972,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -1052,7 +996,7 @@
       </c>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1074,61 +1018,55 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="11" t="s">
+    <row r="14" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="2">
         <v>5</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="11" t="s">
+    </row>
+    <row r="15" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="2">
         <v>13</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -1152,7 +1090,7 @@
       </c>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -1174,7 +1112,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
@@ -1198,7 +1136,7 @@
       </c>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -1218,39 +1156,33 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="11" t="s">
+    <row r="20" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="2">
         <v>19</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I20" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J20" s="14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -1272,7 +1204,7 @@
       <c r="G21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="8" t="s">
         <v>65</v>
       </c>
     </row>

--- a/Projektleitung/ProjektStu.xlsx
+++ b/Projektleitung/ProjektStu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zeiss-my.sharepoint.com/personal/nico_hoehn_zeiss_com/Documents/Microsoft Teams-Chatdateien/desktop/Stu/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/02520db892aadeb1/Dokumente/GitHub/the-machine-learning-brick/Projektleitung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{B10DB337-5233-4793-ACC1-40FBA2BF6423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FD1EC56-4219-4D38-814D-45A03D40906F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="114_{0B9A8477-981E-46D8-BAF3-EDBA0CF131E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DBC8F7FF-C9D8-41D1-8461-80D8FB4B8939}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DBC8F7FF-C9D8-41D1-8461-80D8FB4B8939}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
